--- a/doctool/test/auto/scenario24/システム機能設計書_サンプル_S24_expected.xlsx
+++ b/doctool/test/auto/scenario24/システム機能設計書_サンプル_S24_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\auto\scenario12\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario24\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA135DD6-DAF7-4F54-BE65-22708C846358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42552E3A-E2C4-4123-8DE3-61BC9A6BBA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="4155" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー結果1回目" sheetId="9" r:id="rId1"/>
@@ -1377,7 +1377,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S12</t>
+    <t>システム機能設計書_サンプル_S24</t>
   </si>
   <si>
     <t>B5</t>
@@ -1512,7 +1512,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="&quot;第&quot;0.00&quot;版&quot;"/>
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="181" formatCode="#"/>
+    <numFmt numFmtId="178" formatCode="#"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -2933,25 +2933,25 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="10" xfId="11" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="10" xfId="11" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="22" fillId="9" borderId="10" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="22" fillId="9" borderId="10" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="22" fillId="9" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="178" fontId="22" fillId="9" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="22" fillId="9" borderId="10" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="22" fillId="9" borderId="10" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="22" fillId="9" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="22" fillId="9" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="22" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
@@ -3429,7 +3429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5940AD8-44B4-459D-97FB-BD6E1ABE64A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3065BD4B-56B2-4CCA-B36E-BEC1FB014BC7}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4940,23 +4940,23 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{3A2B1759-C8CA-424F-AB26-7FA8A3973921}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{833E83EC-B982-4961-B4FE-CCA56851D5DE}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{9B0313C6-B6FD-4314-8EAA-87FC0C4CA832}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{3BC207F6-A2F3-4E64-9CEA-995D40269515}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{8FF3D317-62FA-4189-B631-45B4990C8A49}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{2169D7D9-2877-4535-87F7-3AA6B61A45CD}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{AA1412A5-4582-47A1-8668-FEB67B879B6E}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{876F8D34-74F0-4797-9F4B-CC522C302864}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{9B07F365-5E3C-4F20-9EA2-30719A1246EF}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{A87B81BD-190C-4FE7-9113-24FE4632AF7A}"/>
-    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{8B8A979E-B228-4E5F-A192-76E4B9A2137F}"/>
-    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{202B99C6-2A84-4550-B25D-95DA0A12F148}"/>
-    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{6E3764F9-9344-417B-81C7-700522190C45}"/>
-    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{8AF402E1-5047-48DB-8E06-D973E7F36EC0}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{1CC17C0F-43A2-454F-BF48-CF0D0AF9E338}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{12142139-085B-4E70-BBEF-B0FDA797183B}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{2774D6D3-B063-4834-8E2C-7BB8AA33E853}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{FAB5A6C3-2214-4012-B117-61349EB949AD}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{B5A1F530-E3FB-4E87-A4CA-1837A3EE0EDF}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{E7479DC9-5A59-410C-B65F-5F304E92D08C}"/>
+    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{D924F07E-7B2E-400A-8EB3-A72C4FC70B94}"/>
+    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{8407E96A-6AA2-4483-AB79-41601F0EBE63}"/>
+    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{ED2CF6D0-4EE6-400A-9915-D82A6CFFE74F}"/>
+    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{BD7EF554-7762-4DA2-A016-41EBB7EC9B5E}"/>
+    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{F1B79E72-E73B-43C1-9818-E983174744D5}"/>
+    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{3452EE7F-328E-4687-9CB2-0A92A5B549F4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="67" orientation="landscape" verticalDpi="200" r:id="rId1"/>

--- a/doctool/test/auto/scenario24/システム機能設計書_サンプル_S24_expected.xlsx
+++ b/doctool/test/auto/scenario24/システム機能設計書_サンプル_S24_expected.xlsx
@@ -5,39 +5,40 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario24\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario23\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42552E3A-E2C4-4123-8DE3-61BC9A6BBA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B97882-D93F-4126-9A46-6636EFB12B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="レビュー結果1回目" sheetId="9" r:id="rId1"/>
-    <sheet name="表紙" sheetId="1" r:id="rId2"/>
-    <sheet name="変更履歴" sheetId="2" r:id="rId3"/>
-    <sheet name="目次" sheetId="3" r:id="rId4"/>
-    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId5"/>
-    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId6"/>
-    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId7"/>
-    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId8"/>
-    <sheet name="データ" sheetId="8" state="hidden" r:id="rId9"/>
+    <sheet name="エラーシート" sheetId="10" r:id="rId1"/>
+    <sheet name="レビュー結果1回目" sheetId="9" r:id="rId2"/>
+    <sheet name="表紙" sheetId="1" r:id="rId3"/>
+    <sheet name="変更履歴" sheetId="2" r:id="rId4"/>
+    <sheet name="目次" sheetId="3" r:id="rId5"/>
+    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId6"/>
+    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId7"/>
+    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId8"/>
+    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId9"/>
+    <sheet name="データ" sheetId="8" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_Toc46209822" localSheetId="4">'1.  画面取引定義'!$B$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'1.  画面取引定義'!$A$1:$AI$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">データ!$A$1:$E$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー結果1回目!$A$1:$N$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">表紙!$A$1:$S$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">目次!$A$1:$AI$33</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'1.  画面取引定義'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
+    <definedName name="_Toc46209822" localSheetId="5">'1.  画面取引定義'!$B$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'1.  画面取引定義'!$A$1:$AI$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">データ!$A$1:$E$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー結果1回目!$A$1:$K$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">表紙!$A$1:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">目次!$A$1:$AI$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'1.  画面取引定義'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
     <definedName name="引継項目格納先">データ!$B$2:$B$2</definedName>
     <definedName name="画面項目種類">データ!$A$2:$A$14</definedName>
     <definedName name="種別一覧">データ!$C$2:$C$7</definedName>
@@ -99,7 +100,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="E60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+    <comment ref="D50" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:z
+未登録カテゴリの指摘コメントの例。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -115,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
@@ -133,119 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E63" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:d
-機能・仕様誤りの指摘例（カテゴリd）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E64" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:e
-設計・ドキュメント規約違反の指摘例（カテゴリe）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E65" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:f
-記述誤りの指摘例（カテゴリf）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E66" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:g
-疑問点・確認の指摘例（カテゴリg）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:h
-改善要望の指摘例（カテゴリh）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E68" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:i
-仕様変更の指摘例（カテゴリi）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E69" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:j
-テスト項目漏れの指摘例（カテゴリj）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E70" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:k
-テスト漏れの指摘例（カテゴリk）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000D000000}">
+    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
       <text>
         <r>
           <rPr>
@@ -259,26 +162,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E71" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:l
-その他の指摘例（カテゴリl）。</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="323">
   <si>
     <t>第１．２版</t>
   </si>
@@ -1228,18 +1117,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>j</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>k</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>l</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>対応状況</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
@@ -1286,18 +1163,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>94_テスト項目漏れ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>95_テスト漏れ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>96_その他</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>計</t>
     <rPh sb="0" eb="1">
       <t>ケイ</t>
@@ -1377,7 +1242,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S24</t>
+    <t>システム機能設計書_サンプル_S23</t>
   </si>
   <si>
     <t>B5</t>
@@ -1395,6 +1260,23 @@
   </si>
   <si>
     <t>未</t>
+  </si>
+  <si>
+    <t>＜エラー＞</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>エラー内容</t>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>未登録の指摘分類エイリアスが記入されています: z</t>
+  </si>
+  <si>
+    <t>2. WA1020101(プロジェクト登録画面)'!$D$50</t>
   </si>
   <si>
     <t>E60</t>
@@ -1422,87 +1304,6 @@
   </si>
   <si>
     <t>済</t>
-  </si>
-  <si>
-    <t>E63</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>機能・仕様誤りの指摘例（カテゴリd）。</t>
-  </si>
-  <si>
-    <t>E64</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>設計・ドキュメント規約違反の指摘例（カテゴリe）。</t>
-  </si>
-  <si>
-    <t>E65</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>記述誤りの指摘例（カテゴリf）。</t>
-  </si>
-  <si>
-    <t>E66</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>疑問点・確認の指摘例（カテゴリg）。</t>
-  </si>
-  <si>
-    <t>E67</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>改善要望の指摘例（カテゴリh）。</t>
-  </si>
-  <si>
-    <t>E68</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>仕様変更の指摘例（カテゴリi）。</t>
-  </si>
-  <si>
-    <t>E69</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>テスト項目漏れの指摘例（カテゴリj）。</t>
-  </si>
-  <si>
-    <t>E70</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>テスト漏れの指摘例（カテゴリk）。</t>
-  </si>
-  <si>
-    <t>E71</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>その他の指摘例（カテゴリl）。</t>
   </si>
 </sst>
 </file>
@@ -2224,7 +2025,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="302">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2927,9 +2728,6 @@
     <xf numFmtId="0" fontId="26" fillId="8" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2939,16 +2737,10 @@
     <xf numFmtId="178" fontId="22" fillId="9" borderId="10" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="22" fillId="9" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="22" fillId="9" borderId="10" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="22" fillId="9" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2993,6 +2785,10 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="11" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" quotePrefix="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -3429,31 +3225,214 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3065BD4B-56B2-4CCA-B36E-BEC1FB014BC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB5C215-5415-4123-8166-0557F0C27D3E}">
+  <sheetPr codeName="ErrorSheetTemplate">
+    <tabColor theme="3" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="105.1640625" style="287" customWidth="1"/>
+    <col min="2" max="2" width="42.1640625" style="262" customWidth="1"/>
+    <col min="3" max="16384" width="9.33203125" style="262"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A1" s="286" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" s="287" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="262" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" s="287" t="s">
+        <v>314</v>
+      </c>
+      <c r="B3" s="299" t="s">
+        <v>315</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10"/>
+  <hyperlinks>
+    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$D$50" display="'2. WA1020101(プロジェクト登録画面)'!$D$50" xr:uid="{64D2E460-D4DB-4BC9-86C1-F753380C7804}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Sheet6">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="52" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="52" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="52" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="52" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="52" t="s">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC2E0AF-3204-4CF9-B73A-EABAF4691733}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="262"/>
-    <col min="2" max="14" width="17.6640625" style="262" customWidth="1"/>
-    <col min="15" max="26" width="4.5" style="262" customWidth="1"/>
-    <col min="27" max="27" width="98.1640625" style="262" customWidth="1"/>
-    <col min="28" max="16384" width="9.33203125" style="262"/>
+    <col min="2" max="11" width="17.6640625" style="262" customWidth="1"/>
+    <col min="12" max="20" width="4.5" style="262" customWidth="1"/>
+    <col min="21" max="21" width="98.1640625" style="262" customWidth="1"/>
+    <col min="22" max="16384" width="9.33203125" style="262"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A1" s="261" t="s">
         <v>265</v>
       </c>
-      <c r="O1" s="263"/>
-      <c r="AA1" s="264" t="s">
+      <c r="L1" s="263"/>
+      <c r="U1" s="264" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A2" s="262" t="s">
         <v>267</v>
       </c>
@@ -3464,9 +3443,9 @@
       <c r="G2" s="266"/>
       <c r="H2" s="266"/>
       <c r="I2" s="267"/>
-      <c r="O2" s="263"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="L2" s="263"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A3" s="268" t="s">
         <v>269</v>
       </c>
@@ -3488,9 +3467,9 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A4" s="271" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B4" s="271"/>
       <c r="C4" s="272">
@@ -3512,12 +3491,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="261" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B7" s="276" t="s">
         <v>277</v>
       </c>
@@ -3545,394 +3524,304 @@
       <c r="J7" s="270" t="s">
         <v>285</v>
       </c>
-      <c r="K7" s="270" t="s">
+    </row>
+    <row r="8" spans="1:21" ht="27" x14ac:dyDescent="0.15">
+      <c r="A8" s="269" t="s">
         <v>286</v>
       </c>
-      <c r="L7" s="270" t="s">
+      <c r="B8" s="277" t="s">
         <v>287</v>
       </c>
-      <c r="M7" s="270" t="s">
+      <c r="C8" s="277" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="27" x14ac:dyDescent="0.15">
-      <c r="A8" s="269" t="s">
+      <c r="D8" s="277" t="s">
         <v>289</v>
       </c>
-      <c r="B8" s="277" t="s">
+      <c r="E8" s="278" t="s">
         <v>290</v>
       </c>
-      <c r="C8" s="277" t="s">
+      <c r="F8" s="277" t="s">
         <v>291</v>
       </c>
-      <c r="D8" s="277" t="s">
+      <c r="G8" s="277" t="s">
         <v>292</v>
       </c>
-      <c r="E8" s="278" t="s">
+      <c r="H8" s="277" t="s">
         <v>293</v>
       </c>
-      <c r="F8" s="277" t="s">
+      <c r="I8" s="277" t="s">
         <v>294</v>
       </c>
-      <c r="G8" s="277" t="s">
+      <c r="J8" s="278" t="s">
         <v>295</v>
       </c>
-      <c r="H8" s="277" t="s">
+      <c r="K8" s="279" t="s">
         <v>296</v>
       </c>
-      <c r="I8" s="277" t="s">
-        <v>297</v>
-      </c>
-      <c r="J8" s="278" t="s">
-        <v>298</v>
-      </c>
-      <c r="K8" s="278" t="s">
-        <v>299</v>
-      </c>
-      <c r="L8" s="278" t="s">
-        <v>300</v>
-      </c>
-      <c r="M8" s="278" t="s">
-        <v>301</v>
-      </c>
-      <c r="N8" s="279" t="s">
-        <v>302</v>
-      </c>
+      <c r="L8" s="280"/>
+      <c r="M8" s="280"/>
+      <c r="N8" s="280"/>
       <c r="O8" s="280"/>
       <c r="P8" s="280"/>
       <c r="Q8" s="280"/>
-      <c r="R8" s="281"/>
-      <c r="S8" s="281"/>
-      <c r="T8" s="281"/>
-      <c r="U8" s="281"/>
-      <c r="V8" s="281"/>
-      <c r="W8" s="281"/>
-      <c r="X8" s="281"/>
-      <c r="Y8" s="281"/>
-      <c r="Z8" s="281"/>
-      <c r="AA8" s="281"/>
-      <c r="AB8" s="281"/>
-      <c r="AC8" s="281"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="R8" s="280"/>
+      <c r="S8" s="280"/>
+      <c r="T8" s="280"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A9" s="269" t="s">
-        <v>303</v>
-      </c>
-      <c r="B9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,O15:O27)=0,"",SUMIF($K15:$K27,$A9,O15:O27))</f>
+        <v>297</v>
+      </c>
+      <c r="B9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A9,L15:L18)=0,"",SUMIF($K15:$K18,$A9,L15:L18))</f>
         <v/>
       </c>
-      <c r="C9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,P15:P27)=0,"",SUMIF($K15:$K27,$A9,P15:P27))</f>
+      <c r="C9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A9,M15:M18)=0,"",SUMIF($K15:$K18,$A9,M15:M18))</f>
         <v/>
       </c>
-      <c r="D9" s="282">
-        <f>IF(SUMIF($K15:$K27,$A9,Q15:Q27)=0,"",SUMIF($K15:$K27,$A9,Q15:Q27))</f>
+      <c r="D9" s="281">
+        <f>IF(SUMIF($K15:$K18,$A9,N15:N18)=0,"",SUMIF($K15:$K18,$A9,N15:N18))</f>
         <v>1</v>
       </c>
-      <c r="E9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,R15:R27)=0,"",SUMIF($K15:$K27,$A9,R15:R27))</f>
+      <c r="E9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A9,O15:O18)=0,"",SUMIF($K15:$K18,$A9,O15:O18))</f>
         <v/>
       </c>
-      <c r="F9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,S15:S27)=0,"",SUMIF($K15:$K27,$A9,S15:S27))</f>
+      <c r="F9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A9,P15:P18)=0,"",SUMIF($K15:$K18,$A9,P15:P18))</f>
         <v/>
       </c>
-      <c r="G9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,T15:T27)=0,"",SUMIF($K15:$K27,$A9,T15:T27))</f>
+      <c r="G9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A9,Q15:Q18)=0,"",SUMIF($K15:$K18,$A9,Q15:Q18))</f>
         <v/>
       </c>
-      <c r="H9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,U15:U27)=0,"",SUMIF($K15:$K27,$A9,U15:U27))</f>
+      <c r="H9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A9,R15:R18)=0,"",SUMIF($K15:$K18,$A9,R15:R18))</f>
         <v/>
       </c>
-      <c r="I9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,V15:V27)=0,"",SUMIF($K15:$K27,$A9,V15:V27))</f>
+      <c r="I9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A9,S15:S18)=0,"",SUMIF($K15:$K18,$A9,S15:S18))</f>
         <v/>
       </c>
-      <c r="J9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,W15:W27)=0,"",SUMIF($K15:$K27,$A9,W15:W27))</f>
+      <c r="J9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A9,T15:T18)=0,"",SUMIF($K15:$K18,$A9,T15:T18))</f>
         <v/>
       </c>
-      <c r="K9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,X15:X27)=0,"",SUMIF($K15:$K27,$A9,X15:X27))</f>
-        <v/>
-      </c>
-      <c r="L9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,Y15:Y27)=0,"",SUMIF($K15:$K27,$A9,Y15:Y27))</f>
-        <v/>
-      </c>
-      <c r="M9" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,Z15:Z27)=0,"",SUMIF($K15:$K27,$A9,Z15:Z27))</f>
-        <v/>
-      </c>
-      <c r="N9" s="283">
-        <f>SUM(B9:M9)</f>
+      <c r="K9" s="282">
+        <f>SUM(B9:J9)</f>
         <v>1</v>
       </c>
-      <c r="O9" s="284"/>
-      <c r="P9" s="284"/>
-      <c r="Q9" s="284"/>
+      <c r="L9" s="261"/>
+      <c r="M9" s="261"/>
+      <c r="N9" s="261"/>
+      <c r="O9" s="261"/>
+      <c r="P9" s="261"/>
+      <c r="Q9" s="261"/>
       <c r="R9" s="261"/>
       <c r="S9" s="261"/>
       <c r="T9" s="261"/>
-      <c r="U9" s="261"/>
-      <c r="V9" s="261"/>
-      <c r="W9" s="261"/>
-      <c r="X9" s="261"/>
-      <c r="Y9" s="261"/>
-      <c r="Z9" s="261"/>
-      <c r="AA9" s="261"/>
-      <c r="AB9" s="261"/>
-      <c r="AC9" s="261"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A10" s="269" t="s">
-        <v>304</v>
-      </c>
-      <c r="B10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,O15:O27)=0,"",SUMIF($K15:$K27,$A10,O15:O27))</f>
+        <v>298</v>
+      </c>
+      <c r="B10" s="281">
+        <f>IF(SUMIF($K15:$K18,$A10,L15:L18)=0,"",SUMIF($K15:$K18,$A10,L15:L18))</f>
         <v>1</v>
       </c>
-      <c r="C10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,P15:P27)=0,"",SUMIF($K15:$K27,$A10,P15:P27))</f>
+      <c r="C10" s="281">
+        <f>IF(SUMIF($K15:$K18,$A10,M15:M18)=0,"",SUMIF($K15:$K18,$A10,M15:M18))</f>
         <v>1</v>
       </c>
-      <c r="D10" s="282" t="str">
-        <f>IF(SUMIF($K15:$K27,$A10,Q15:Q27)=0,"",SUMIF($K15:$K27,$A10,Q15:Q27))</f>
+      <c r="D10" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A10,N15:N18)=0,"",SUMIF($K15:$K18,$A10,N15:N18))</f>
         <v/>
       </c>
-      <c r="E10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,R15:R27)=0,"",SUMIF($K15:$K27,$A10,R15:R27))</f>
-        <v>1</v>
-      </c>
-      <c r="F10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,S15:S27)=0,"",SUMIF($K15:$K27,$A10,S15:S27))</f>
-        <v>1</v>
-      </c>
-      <c r="G10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,T15:T27)=0,"",SUMIF($K15:$K27,$A10,T15:T27))</f>
-        <v>1</v>
-      </c>
-      <c r="H10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,U15:U27)=0,"",SUMIF($K15:$K27,$A10,U15:U27))</f>
-        <v>1</v>
-      </c>
-      <c r="I10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,V15:V27)=0,"",SUMIF($K15:$K27,$A10,V15:V27))</f>
-        <v>1</v>
-      </c>
-      <c r="J10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,W15:W27)=0,"",SUMIF($K15:$K27,$A10,W15:W27))</f>
-        <v>1</v>
+      <c r="E10" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A10,O15:O18)=0,"",SUMIF($K15:$K18,$A10,O15:O18))</f>
+        <v/>
+      </c>
+      <c r="F10" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A10,P15:P18)=0,"",SUMIF($K15:$K18,$A10,P15:P18))</f>
+        <v/>
+      </c>
+      <c r="G10" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A10,Q15:Q18)=0,"",SUMIF($K15:$K18,$A10,Q15:Q18))</f>
+        <v/>
+      </c>
+      <c r="H10" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A10,R15:R18)=0,"",SUMIF($K15:$K18,$A10,R15:R18))</f>
+        <v/>
+      </c>
+      <c r="I10" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A10,S15:S18)=0,"",SUMIF($K15:$K18,$A10,S15:S18))</f>
+        <v/>
+      </c>
+      <c r="J10" s="281" t="str">
+        <f>IF(SUMIF($K15:$K18,$A10,T15:T18)=0,"",SUMIF($K15:$K18,$A10,T15:T18))</f>
+        <v/>
       </c>
       <c r="K10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,X15:X27)=0,"",SUMIF($K15:$K27,$A10,X15:X27))</f>
-        <v>1</v>
-      </c>
-      <c r="L10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,Y15:Y27)=0,"",SUMIF($K15:$K27,$A10,Y15:Y27))</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="282">
-        <f>IF(SUMIF($K15:$K27,$A10,Z15:Z27)=0,"",SUMIF($K15:$K27,$A10,Z15:Z27))</f>
-        <v>1</v>
-      </c>
-      <c r="N10" s="283">
-        <f>SUM(B10:M10)</f>
-        <v>11</v>
-      </c>
-      <c r="O10" s="284"/>
-      <c r="P10" s="284"/>
-      <c r="Q10" s="284"/>
+        <f>SUM(B10:J10)</f>
+        <v>2</v>
+      </c>
+      <c r="L10" s="261"/>
+      <c r="M10" s="261"/>
+      <c r="N10" s="261"/>
+      <c r="O10" s="261"/>
+      <c r="P10" s="261"/>
+      <c r="Q10" s="261"/>
       <c r="R10" s="261"/>
       <c r="S10" s="261"/>
       <c r="T10" s="261"/>
-      <c r="U10" s="261"/>
-      <c r="V10" s="261"/>
-      <c r="W10" s="261"/>
-      <c r="X10" s="261"/>
-      <c r="Y10" s="261"/>
-      <c r="Z10" s="261"/>
-      <c r="AA10" s="261"/>
-      <c r="AB10" s="261"/>
-      <c r="AC10" s="261"/>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A11" s="285" t="s">
-        <v>302</v>
-      </c>
-      <c r="B11" s="286">
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A11" s="283" t="s">
+        <v>296</v>
+      </c>
+      <c r="B11" s="284">
         <f>SUM(B9:B10)</f>
         <v>1</v>
       </c>
-      <c r="C11" s="286">
-        <f t="shared" ref="C11:M11" si="0">SUM(C9:C10)</f>
+      <c r="C11" s="284">
+        <f t="shared" ref="C11:K11" si="0">SUM(C9:C10)</f>
         <v>1</v>
       </c>
-      <c r="D11" s="286">
+      <c r="D11" s="284">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E11" s="286">
+      <c r="E11" s="284">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F11" s="286">
+        <v>0</v>
+      </c>
+      <c r="F11" s="284">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G11" s="286">
+        <v>0</v>
+      </c>
+      <c r="G11" s="284">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H11" s="286">
+        <v>0</v>
+      </c>
+      <c r="H11" s="284">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I11" s="286">
+        <v>0</v>
+      </c>
+      <c r="I11" s="284">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J11" s="286">
+        <v>0</v>
+      </c>
+      <c r="J11" s="284">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K11" s="286">
+        <v>0</v>
+      </c>
+      <c r="K11" s="284">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L11" s="286">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="286">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N11" s="286">
-        <f>SUM(B11:M11)</f>
-        <v>12</v>
-      </c>
-      <c r="O11" s="287"/>
-      <c r="P11" s="287"/>
-      <c r="Q11" s="287"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A12" s="261"/>
-      <c r="B12" s="288"/>
-      <c r="C12" s="288"/>
-      <c r="D12" s="288"/>
-      <c r="E12" s="288"/>
-      <c r="F12" s="288"/>
-      <c r="G12" s="288"/>
-      <c r="H12" s="288"/>
-      <c r="I12" s="288"/>
-      <c r="J12" s="288"/>
-      <c r="K12" s="288"/>
-      <c r="L12" s="288"/>
-      <c r="M12" s="288"/>
-      <c r="N12" s="288"/>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A13" s="289" t="s">
-        <v>305</v>
-      </c>
-      <c r="B13" s="290"/>
-      <c r="C13" s="290"/>
-      <c r="D13" s="290"/>
-      <c r="F13" s="290"/>
-      <c r="O13" s="263" t="s">
-        <v>306</v>
-      </c>
+      <c r="B12" s="285"/>
+      <c r="C12" s="285"/>
+      <c r="D12" s="285"/>
+      <c r="E12" s="285"/>
+      <c r="F12" s="285"/>
+      <c r="G12" s="285"/>
+      <c r="H12" s="285"/>
+      <c r="I12" s="285"/>
+      <c r="J12" s="285"/>
+      <c r="K12" s="285"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A13" s="286" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="287"/>
+      <c r="C13" s="287"/>
+      <c r="D13" s="287"/>
+      <c r="F13" s="287"/>
+      <c r="L13" s="263" t="s">
+        <v>300</v>
+      </c>
+      <c r="M13" s="263"/>
+      <c r="N13" s="263"/>
+      <c r="O13" s="263"/>
       <c r="P13" s="263"/>
       <c r="Q13" s="263"/>
       <c r="R13" s="263"/>
       <c r="S13" s="263"/>
       <c r="T13" s="263"/>
-      <c r="U13" s="263"/>
-      <c r="V13" s="263"/>
-      <c r="W13" s="263"/>
-      <c r="X13" s="263"/>
-      <c r="Y13" s="263"/>
-      <c r="Z13" s="263"/>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A14" s="291" t="s">
-        <v>307</v>
-      </c>
-      <c r="B14" s="291" t="s">
-        <v>308</v>
-      </c>
-      <c r="C14" s="291" t="s">
-        <v>309</v>
-      </c>
-      <c r="D14" s="291" t="s">
-        <v>310</v>
-      </c>
-      <c r="E14" s="292" t="s">
-        <v>311</v>
-      </c>
-      <c r="F14" s="293"/>
-      <c r="G14" s="294"/>
-      <c r="H14" s="294"/>
-      <c r="I14" s="294"/>
-      <c r="J14" s="295"/>
-      <c r="K14" s="296" t="s">
-        <v>289</v>
-      </c>
-      <c r="O14" s="297" t="s">
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A14" s="288" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" s="288" t="s">
+        <v>302</v>
+      </c>
+      <c r="C14" s="288" t="s">
+        <v>303</v>
+      </c>
+      <c r="D14" s="288" t="s">
+        <v>304</v>
+      </c>
+      <c r="E14" s="289" t="s">
+        <v>305</v>
+      </c>
+      <c r="F14" s="290"/>
+      <c r="G14" s="291"/>
+      <c r="H14" s="291"/>
+      <c r="I14" s="291"/>
+      <c r="J14" s="292"/>
+      <c r="K14" s="293" t="s">
+        <v>286</v>
+      </c>
+      <c r="L14" s="294" t="s">
         <v>277</v>
       </c>
-      <c r="P14" s="297" t="s">
+      <c r="M14" s="294" t="s">
         <v>278</v>
       </c>
-      <c r="Q14" s="297" t="s">
+      <c r="N14" s="294" t="s">
         <v>279</v>
       </c>
-      <c r="R14" s="297" t="s">
+      <c r="O14" s="294" t="s">
         <v>280</v>
       </c>
-      <c r="S14" s="297" t="s">
+      <c r="P14" s="294" t="s">
         <v>281</v>
       </c>
-      <c r="T14" s="297" t="s">
+      <c r="Q14" s="294" t="s">
         <v>282</v>
       </c>
-      <c r="U14" s="297" t="s">
+      <c r="R14" s="294" t="s">
         <v>283</v>
       </c>
-      <c r="V14" s="297" t="s">
+      <c r="S14" s="294" t="s">
         <v>284</v>
       </c>
-      <c r="W14" s="297" t="s">
+      <c r="T14" s="294" t="s">
         <v>285</v>
       </c>
-      <c r="X14" s="297" t="s">
-        <v>286</v>
-      </c>
-      <c r="Y14" s="297" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z14" s="297" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="40.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:21" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A15" s="272" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="300" t="s">
-        <v>313</v>
+      <c r="B15" s="297" t="s">
+        <v>307</v>
       </c>
       <c r="C15" s="272" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D15" s="272" t="s">
-        <v>315</v>
-      </c>
-      <c r="E15" s="301" t="s">
-        <v>316</v>
+        <v>309</v>
+      </c>
+      <c r="E15" s="298" t="s">
+        <v>310</v>
       </c>
       <c r="F15" s="271"/>
       <c r="G15" s="271"/>
@@ -3940,78 +3829,66 @@
       <c r="I15" s="271"/>
       <c r="J15" s="271"/>
       <c r="K15" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O15" s="298">
-        <f t="shared" ref="O15:Z27" si="1">IF($D15=O$14,1,0)</f>
+        <v>311</v>
+      </c>
+      <c r="L15" s="295">
+        <f t="shared" ref="L15:T18" si="1">IF($D15=L$14,1,0)</f>
         <v>1</v>
       </c>
-      <c r="P15" s="298">
+      <c r="M15" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="298">
+      <c r="N15" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R15" s="298">
+      <c r="O15" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S15" s="298">
+      <c r="P15" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T15" s="298">
+      <c r="Q15" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U15" s="298">
+      <c r="R15" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V15" s="298">
+      <c r="S15" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W15" s="298">
+      <c r="T15" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X15" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="299" t="str">
+      <c r="U15" s="296" t="str">
         <f>IF(E15&lt;&gt;"",E15,"")</f>
         <v>レビュー指摘コメントの例。
 自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。
 ※レビュー日時を書く場合はコロンの直後に*を書く。</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:21" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A16" s="272" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="300" t="s">
+      <c r="B16" s="297" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" s="272" t="s">
+        <v>308</v>
+      </c>
+      <c r="D16" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="E16" s="298" t="s">
         <v>318</v>
-      </c>
-      <c r="C16" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D16" s="272" t="s">
-        <v>319</v>
-      </c>
-      <c r="E16" s="301" t="s">
-        <v>320</v>
       </c>
       <c r="F16" s="271"/>
       <c r="G16" s="271"/>
@@ -4019,78 +3896,66 @@
       <c r="I16" s="271"/>
       <c r="J16" s="271"/>
       <c r="K16" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O16" s="298">
+        <v>311</v>
+      </c>
+      <c r="L16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P16" s="298">
+      <c r="M16" s="295">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q16" s="298">
+      <c r="N16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R16" s="298">
+      <c r="O16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S16" s="298">
+      <c r="P16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T16" s="298">
+      <c r="Q16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U16" s="298">
+      <c r="R16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V16" s="298">
+      <c r="S16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W16" s="298">
+      <c r="T16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X16" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="299" t="str">
+      <c r="U16" s="296" t="str">
         <f>IF(E16&lt;&gt;"",E16,"")</f>
         <v>対応内容の例。
 ---
 対応内容はデリミタ（---）の後に記入する。</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A17" s="272" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="300" t="s">
+      <c r="B17" s="297" t="s">
+        <v>319</v>
+      </c>
+      <c r="C17" s="272" t="s">
+        <v>308</v>
+      </c>
+      <c r="D17" s="272" t="s">
+        <v>320</v>
+      </c>
+      <c r="E17" s="298" t="s">
         <v>321</v>
-      </c>
-      <c r="C17" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D17" s="272" t="s">
-        <v>322</v>
-      </c>
-      <c r="E17" s="301" t="s">
-        <v>323</v>
       </c>
       <c r="F17" s="271"/>
       <c r="G17" s="271"/>
@@ -4098,57 +3963,45 @@
       <c r="I17" s="271"/>
       <c r="J17" s="271"/>
       <c r="K17" s="272" t="s">
-        <v>324</v>
-      </c>
-      <c r="O17" s="298">
+        <v>322</v>
+      </c>
+      <c r="L17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P17" s="298">
+      <c r="M17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="298">
+      <c r="N17" s="295">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R17" s="298">
+      <c r="O17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S17" s="298">
+      <c r="P17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T17" s="298">
+      <c r="Q17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U17" s="298">
+      <c r="R17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V17" s="298">
+      <c r="S17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="298">
+      <c r="T17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X17" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="299" t="str">
+      <c r="U17" s="296" t="str">
         <f>IF(E17&lt;&gt;"",E17,"")</f>
         <v>対応内容を確認し、指摘をクローズする例。
 ---
@@ -4157,814 +4010,91 @@
 08/02山田 済</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A18" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="300" t="s">
-        <v>325</v>
-      </c>
-      <c r="C18" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D18" s="272" t="s">
-        <v>326</v>
-      </c>
-      <c r="E18" s="271" t="s">
-        <v>327</v>
-      </c>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A18" s="272"/>
+      <c r="B18" s="272"/>
+      <c r="C18" s="272"/>
+      <c r="D18" s="272"/>
+      <c r="E18" s="271"/>
       <c r="F18" s="271"/>
       <c r="G18" s="271"/>
       <c r="H18" s="271"/>
       <c r="I18" s="271"/>
       <c r="J18" s="271"/>
-      <c r="K18" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O18" s="298">
+      <c r="K18" s="272"/>
+      <c r="L18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P18" s="298">
+      <c r="M18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="298">
+      <c r="N18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R18" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S18" s="298">
+      <c r="O18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T18" s="298">
+      <c r="P18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U18" s="298">
+      <c r="Q18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V18" s="298">
+      <c r="R18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W18" s="298">
+      <c r="S18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X18" s="298">
+      <c r="T18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y18" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="299" t="str">
+      <c r="U18" s="296" t="str">
         <f>IF(E18&lt;&gt;"",E18,"")</f>
-        <v>機能・仕様誤りの指摘例（カテゴリd）。</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A19" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="300" t="s">
-        <v>328</v>
-      </c>
-      <c r="C19" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D19" s="272" t="s">
-        <v>329</v>
-      </c>
-      <c r="E19" s="271" t="s">
-        <v>330</v>
-      </c>
-      <c r="F19" s="271"/>
-      <c r="G19" s="271"/>
-      <c r="H19" s="271"/>
-      <c r="I19" s="271"/>
-      <c r="J19" s="271"/>
-      <c r="K19" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="299" t="str">
-        <f>IF(E19&lt;&gt;"",E19,"")</f>
-        <v>設計・ドキュメント規約違反の指摘例（カテゴリe）。</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A20" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="300" t="s">
-        <v>331</v>
-      </c>
-      <c r="C20" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D20" s="272" t="s">
-        <v>332</v>
-      </c>
-      <c r="E20" s="271" t="s">
-        <v>333</v>
-      </c>
-      <c r="F20" s="271"/>
-      <c r="G20" s="271"/>
-      <c r="H20" s="271"/>
-      <c r="I20" s="271"/>
-      <c r="J20" s="271"/>
-      <c r="K20" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="U20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="299" t="str">
-        <f>IF(E20&lt;&gt;"",E20,"")</f>
-        <v>記述誤りの指摘例（カテゴリf）。</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A21" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="300" t="s">
-        <v>334</v>
-      </c>
-      <c r="C21" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D21" s="272" t="s">
-        <v>335</v>
-      </c>
-      <c r="E21" s="271" t="s">
-        <v>336</v>
-      </c>
-      <c r="F21" s="271"/>
-      <c r="G21" s="271"/>
-      <c r="H21" s="271"/>
-      <c r="I21" s="271"/>
-      <c r="J21" s="271"/>
-      <c r="K21" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z21" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="299" t="str">
-        <f>IF(E21&lt;&gt;"",E21,"")</f>
-        <v>疑問点・確認の指摘例（カテゴリg）。</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A22" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="300" t="s">
-        <v>337</v>
-      </c>
-      <c r="C22" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D22" s="272" t="s">
-        <v>338</v>
-      </c>
-      <c r="E22" s="271" t="s">
-        <v>339</v>
-      </c>
-      <c r="F22" s="271"/>
-      <c r="G22" s="271"/>
-      <c r="H22" s="271"/>
-      <c r="I22" s="271"/>
-      <c r="J22" s="271"/>
-      <c r="K22" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="W22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="299" t="str">
-        <f>IF(E22&lt;&gt;"",E22,"")</f>
-        <v>改善要望の指摘例（カテゴリh）。</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A23" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="300" t="s">
-        <v>340</v>
-      </c>
-      <c r="C23" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D23" s="272" t="s">
-        <v>341</v>
-      </c>
-      <c r="E23" s="271" t="s">
-        <v>342</v>
-      </c>
-      <c r="F23" s="271"/>
-      <c r="G23" s="271"/>
-      <c r="H23" s="271"/>
-      <c r="I23" s="271"/>
-      <c r="J23" s="271"/>
-      <c r="K23" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="X23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA23" s="299" t="str">
-        <f>IF(E23&lt;&gt;"",E23,"")</f>
-        <v>仕様変更の指摘例（カテゴリi）。</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A24" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="300" t="s">
-        <v>343</v>
-      </c>
-      <c r="C24" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D24" s="272" t="s">
-        <v>344</v>
-      </c>
-      <c r="E24" s="271" t="s">
-        <v>345</v>
-      </c>
-      <c r="F24" s="271"/>
-      <c r="G24" s="271"/>
-      <c r="H24" s="271"/>
-      <c r="I24" s="271"/>
-      <c r="J24" s="271"/>
-      <c r="K24" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z24" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA24" s="299" t="str">
-        <f>IF(E24&lt;&gt;"",E24,"")</f>
-        <v>テスト項目漏れの指摘例（カテゴリj）。</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A25" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="300" t="s">
-        <v>346</v>
-      </c>
-      <c r="C25" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D25" s="272" t="s">
-        <v>347</v>
-      </c>
-      <c r="E25" s="271" t="s">
-        <v>348</v>
-      </c>
-      <c r="F25" s="271"/>
-      <c r="G25" s="271"/>
-      <c r="H25" s="271"/>
-      <c r="I25" s="271"/>
-      <c r="J25" s="271"/>
-      <c r="K25" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Z25" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="299" t="str">
-        <f>IF(E25&lt;&gt;"",E25,"")</f>
-        <v>テスト漏れの指摘例（カテゴリk）。</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A26" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="300" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="272" t="s">
-        <v>314</v>
-      </c>
-      <c r="D26" s="272" t="s">
-        <v>350</v>
-      </c>
-      <c r="E26" s="271" t="s">
-        <v>351</v>
-      </c>
-      <c r="F26" s="271"/>
-      <c r="G26" s="271"/>
-      <c r="H26" s="271"/>
-      <c r="I26" s="271"/>
-      <c r="J26" s="271"/>
-      <c r="K26" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="O26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="298">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AA26" s="299" t="str">
-        <f>IF(E26&lt;&gt;"",E26,"")</f>
-        <v>その他の指摘例（カテゴリl）。</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A27" s="272"/>
-      <c r="B27" s="272"/>
-      <c r="C27" s="272"/>
-      <c r="D27" s="272"/>
-      <c r="E27" s="271"/>
-      <c r="F27" s="271"/>
-      <c r="G27" s="271"/>
-      <c r="H27" s="271"/>
-      <c r="I27" s="271"/>
-      <c r="J27" s="271"/>
-      <c r="K27" s="272"/>
-      <c r="O27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z27" s="298">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA27" s="299" t="str">
-        <f>IF(E27&lt;&gt;"",E27,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="E25:J25"/>
-    <mergeCell ref="E26:J26"/>
-    <mergeCell ref="E27:J27"/>
+  <mergeCells count="6">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E15:J15"/>
     <mergeCell ref="E16:J16"/>
     <mergeCell ref="E17:J17"/>
     <mergeCell ref="E18:J18"/>
-    <mergeCell ref="E19:J19"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E21:J21"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
-  <conditionalFormatting sqref="A15:K27">
+  <conditionalFormatting sqref="A15:K18">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>$K15="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{833E83EC-B982-4961-B4FE-CCA56851D5DE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{311D7A0A-E9C9-4F32-8FFF-CF6AD8A51FE5}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{1CC17C0F-43A2-454F-BF48-CF0D0AF9E338}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{12142139-085B-4E70-BBEF-B0FDA797183B}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{2774D6D3-B063-4834-8E2C-7BB8AA33E853}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{FAB5A6C3-2214-4012-B117-61349EB949AD}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{B5A1F530-E3FB-4E87-A4CA-1837A3EE0EDF}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{E7479DC9-5A59-410C-B65F-5F304E92D08C}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{D924F07E-7B2E-400A-8EB3-A72C4FC70B94}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{8407E96A-6AA2-4483-AB79-41601F0EBE63}"/>
-    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{ED2CF6D0-4EE6-400A-9915-D82A6CFFE74F}"/>
-    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{BD7EF554-7762-4DA2-A016-41EBB7EC9B5E}"/>
-    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{F1B79E72-E73B-43C1-9818-E983174744D5}"/>
-    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{3452EE7F-328E-4687-9CB2-0A92A5B549F4}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{F3BFC1F9-C204-4384-8C62-86924A07F334}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{8BFCFE0C-1971-46DF-A117-6DEE36B5CA0F}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{AB8D5EE2-883F-4CA6-AFDB-2DE0E28DC746}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="67" orientation="landscape" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
@@ -5644,7 +4774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
@@ -7205,7 +6335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
@@ -7951,7 +7081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
@@ -8457,7 +7587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet7">
     <pageSetUpPr fitToPage="1"/>
@@ -12758,7 +11888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <pageSetUpPr fitToPage="1"/>
@@ -16277,7 +15407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
@@ -17447,143 +16577,4 @@
     <brk id="33" max="34" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr codeName="Sheet6">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="53" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" s="52" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" s="52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A10" s="52" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A11" s="52" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A12" s="52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A13" s="52" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A14" s="52" t="s">
-        <v>264</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
 </file>
--- a/doctool/test/auto/scenario24/システム機能設計書_サンプル_S24_expected.xlsx
+++ b/doctool/test/auto/scenario24/システム機能設計書_サンプル_S24_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario23\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario24\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B97882-D93F-4126-9A46-6636EFB12B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3A188B-777E-4CAB-B3AE-69FF5D45B7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="エラーシート" sheetId="10" r:id="rId1"/>
@@ -1242,7 +1242,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S23</t>
+    <t>システム機能設計書_サンプル_S24</t>
   </si>
   <si>
     <t>B5</t>
@@ -3225,7 +3225,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB5C215-5415-4123-8166-0557F0C27D3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7C00EDB-A960-4735-9221-DAC350B56EDA}">
   <sheetPr codeName="ErrorSheetTemplate">
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
@@ -3261,7 +3261,7 @@
   </sheetData>
   <phoneticPr fontId="10"/>
   <hyperlinks>
-    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$D$50" display="'2. WA1020101(プロジェクト登録画面)'!$D$50" xr:uid="{64D2E460-D4DB-4BC9-86C1-F753380C7804}"/>
+    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$D$50" display="'2. WA1020101(プロジェクト登録画面)'!$D$50" xr:uid="{BE7EE8A6-B416-4315-A1BB-3FD69C494C18}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3408,7 +3408,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC2E0AF-3204-4CF9-B73A-EABAF4691733}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE7B81A-D61A-4853-909E-6CEAE33E7B06}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4079,14 +4079,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{311D7A0A-E9C9-4F32-8FFF-CF6AD8A51FE5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{1DBECEE2-344A-4669-8DEC-FDCF4CB03ACB}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{F3BFC1F9-C204-4384-8C62-86924A07F334}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{8BFCFE0C-1971-46DF-A117-6DEE36B5CA0F}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{AB8D5EE2-883F-4CA6-AFDB-2DE0E28DC746}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{69C5246E-254B-41AF-88D5-FA196A4921A0}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{D29210F2-CD67-4C8F-B45E-8001F5FF90AB}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{B845E608-6E07-4958-A3E7-5033C203C58D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
